--- a/corr_matrix/residual_exam3C_3PL.xlsx
+++ b/corr_matrix/residual_exam3C_3PL.xlsx
@@ -429,6 +429,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>question_id</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>3C02</t>
@@ -520,49 +525,49 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04974818910135226</v>
+        <v>0.04988829649466472</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.115675865453234</v>
+        <v>-0.1155594374414948</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01221025411013242</v>
+        <v>0.0122507270113682</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.06464115113098513</v>
+        <v>-0.0644856716657479</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.2507540617778997</v>
+        <v>-0.2509520060750661</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01203431481275081</v>
+        <v>0.01199769527737643</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.01026393298187215</v>
+        <v>-0.01039944626945847</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.1331163459317108</v>
+        <v>-0.1332297064404342</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.01987465740946477</v>
+        <v>-0.02023262583688582</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.2124408170959624</v>
+        <v>-0.2123027058448726</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05513312173634611</v>
+        <v>0.05537416099182556</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.05081185705166749</v>
+        <v>-0.05071852943701981</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2399115651769097</v>
+        <v>0.2399073894964485</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01159107370054597</v>
+        <v>0.011760044792132</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.1475681659483614</v>
+        <v>-0.1477357341140219</v>
       </c>
     </row>
     <row r="3">
@@ -572,52 +577,52 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04974818910135226</v>
+        <v>0.04988829649466472</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1142200826127271</v>
+        <v>-0.1138150324523224</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.2557185299315659</v>
+        <v>-0.2557060735642024</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.06707147783368973</v>
+        <v>-0.06770107832964145</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.2352613195572113</v>
+        <v>-0.2351029855145187</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.06803139469126469</v>
+        <v>-0.06831741908233908</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1414613264950851</v>
+        <v>-0.1414459926661722</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.3035463234768049</v>
+        <v>-0.3032569883883089</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1046149505119451</v>
+        <v>0.1047921404974438</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.08171902053233267</v>
+        <v>-0.081502081581056</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.003230615102660938</v>
+        <v>-0.002603634993888561</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.00818018298830407</v>
+        <v>-0.007848159788800862</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1563790222364528</v>
+        <v>0.156493694081298</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1736775005264178</v>
+        <v>0.1739505769284413</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.09772647085232114</v>
+        <v>-0.09751341449245601</v>
       </c>
     </row>
     <row r="4">
@@ -627,52 +632,52 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.115675865453234</v>
+        <v>-0.1155594374414948</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.1142200826127271</v>
+        <v>-0.1138150324523224</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.06867394424733318</v>
+        <v>-0.06878906465468336</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.01947631174672817</v>
+        <v>-0.01872747160022841</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.0957076179404325</v>
+        <v>-0.09588599977257706</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1589755069293717</v>
+        <v>-0.1589483928220262</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1259800681719283</v>
+        <v>0.1259397455857583</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.03256680773346309</v>
+        <v>-0.03264960696369402</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.2551667137727798</v>
+        <v>-0.2559339904157806</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.1548185278472933</v>
+        <v>-0.1544177851719317</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1618051504961168</v>
+        <v>-0.1631356505068055</v>
       </c>
       <c r="N4" t="n">
-        <v>0.02910181453628225</v>
+        <v>0.02933568166165289</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1080459417212321</v>
+        <v>0.1083091976049831</v>
       </c>
       <c r="P4" t="n">
-        <v>0.08450138606341739</v>
+        <v>0.08499193258261718</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1583719064520411</v>
+        <v>0.1582543841509446</v>
       </c>
     </row>
     <row r="5">
@@ -682,52 +687,52 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01221025411013242</v>
+        <v>0.0122507270113682</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.2557185299315659</v>
+        <v>-0.2557060735642024</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.06867394424733318</v>
+        <v>-0.06878906465468336</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1314086953092955</v>
+        <v>-0.1327624798789799</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1800098873739074</v>
+        <v>-0.1803392585936854</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02736063292229577</v>
+        <v>0.02670363295622464</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01075960798367928</v>
+        <v>0.01040818459217854</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1304008297790789</v>
+        <v>-0.1309875693031923</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01588996005253897</v>
+        <v>0.01535182619709805</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.02670355145223416</v>
+        <v>-0.0269627133175299</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1624175403278658</v>
+        <v>-0.1599629804837387</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3132840687800149</v>
+        <v>-0.3135756088197718</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.09164567819270006</v>
+        <v>-0.09183052446789293</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.81620986443648e-05</v>
+        <v>-0.0007493378673589515</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.05125591940290585</v>
+        <v>-0.0524243329062518</v>
       </c>
     </row>
     <row r="6">
@@ -737,52 +742,52 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.06464115113098513</v>
+        <v>-0.0644856716657479</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.06707147783368973</v>
+        <v>-0.06770107832964145</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.01947631174672817</v>
+        <v>-0.01872747160022841</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1314086953092955</v>
+        <v>-0.1327624798789799</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.09908592012101193</v>
+        <v>0.09941567486674668</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.083992756670597</v>
+        <v>-0.08488575652586527</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.01935289473067445</v>
+        <v>-0.02001596018984859</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.04915005551840816</v>
+        <v>-0.0499257608289092</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.2169772356824769</v>
+        <v>-0.2172389265916096</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.06504378092832065</v>
+        <v>-0.06581471079996727</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2320823592345288</v>
+        <v>-0.2286041614346418</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.008296787704363637</v>
+        <v>-0.008960526192506752</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1014316210031799</v>
+        <v>0.1008844494276684</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.1426307552803655</v>
+        <v>-0.143358413067378</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1730098060318544</v>
+        <v>-0.1740479754320955</v>
       </c>
     </row>
     <row r="7">
@@ -792,52 +797,52 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.2507540617778997</v>
+        <v>-0.2509520060750661</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.2352613195572113</v>
+        <v>-0.2351029855145187</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0957076179404325</v>
+        <v>-0.09588599977257706</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1800098873739074</v>
+        <v>-0.1803392585936854</v>
       </c>
       <c r="F7" t="n">
-        <v>0.09908592012101193</v>
+        <v>0.09941567486674668</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.255097316924025</v>
+        <v>0.2552179464369599</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2231254601434112</v>
+        <v>0.2231081922026188</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02735861254493438</v>
+        <v>0.02715367265243016</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.02821436824340161</v>
+        <v>-0.02880036225607209</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.06702146799004474</v>
+        <v>-0.06702500843244734</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0545557848845894</v>
+        <v>0.05461928683228947</v>
       </c>
       <c r="N7" t="n">
-        <v>0.09563706833332421</v>
+        <v>0.09558897275578389</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2800088622062091</v>
+        <v>-0.2799042382213007</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.2232931074821536</v>
+        <v>-0.2232492729314204</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.003477420104303421</v>
+        <v>0.003221320246835839</v>
       </c>
     </row>
     <row r="8">
@@ -847,52 +852,52 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01203431481275081</v>
+        <v>0.01199769527737643</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.06803139469126469</v>
+        <v>-0.06831741908233908</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1589755069293717</v>
+        <v>-0.1589483928220262</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02736063292229577</v>
+        <v>0.02670363295622464</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.083992756670597</v>
+        <v>-0.08488575652586527</v>
       </c>
       <c r="G8" t="n">
-        <v>0.255097316924025</v>
+        <v>0.2552179464369599</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01915593731897594</v>
+        <v>0.01890030023193848</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.008975035573025838</v>
+        <v>-0.009284811555014729</v>
       </c>
       <c r="K8" t="n">
-        <v>0.08037297457869853</v>
+        <v>0.0804204631612911</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.04245124172712152</v>
+        <v>-0.04282791198010744</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.01825900616721546</v>
+        <v>-0.01611205899542008</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.07826192808194926</v>
+        <v>-0.07856538064548585</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1368347571769761</v>
+        <v>-0.1370775365099921</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2704131965250233</v>
+        <v>-0.2707631639220237</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.1712785952862148</v>
+        <v>-0.1717899765930167</v>
       </c>
     </row>
     <row r="9">
@@ -902,52 +907,52 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.01026393298187215</v>
+        <v>-0.01039944626945847</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.1414613264950851</v>
+        <v>-0.1414459926661722</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1259800681719283</v>
+        <v>0.1259397455857583</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01075960798367928</v>
+        <v>0.01040818459217854</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.01935289473067445</v>
+        <v>-0.02001596018984859</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2231254601434112</v>
+        <v>0.2231081922026188</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01915593731897594</v>
+        <v>0.01890030023193848</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.008211315299272054</v>
+        <v>-0.008264968322980801</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0287803870260541</v>
+        <v>0.02874656822736521</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.2855608364447889</v>
+        <v>-0.2856954382706137</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.003660810734103721</v>
+        <v>-0.003096391810210571</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2056830555769451</v>
+        <v>-0.2057101692174151</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.07742031539608377</v>
+        <v>-0.07726734613634824</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2650191617080321</v>
+        <v>-0.26504853568988</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.07427947908520935</v>
+        <v>0.07410866340476774</v>
       </c>
     </row>
     <row r="10">
@@ -957,52 +962,52 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.1331163459317108</v>
+        <v>-0.1332297064404342</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.3035463234768049</v>
+        <v>-0.3032569883883089</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.03256680773346309</v>
+        <v>-0.03264960696369402</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1304008297790789</v>
+        <v>-0.1309875693031923</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.04915005551840816</v>
+        <v>-0.0499257608289092</v>
       </c>
       <c r="G10" t="n">
-        <v>0.02735861254493438</v>
+        <v>0.02715367265243016</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.008975035573025838</v>
+        <v>-0.009284811555014729</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.008211315299272054</v>
+        <v>-0.008264968322980801</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1561978629826447</v>
+        <v>-0.156683766267029</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.06217853777973257</v>
+        <v>-0.06216678817503089</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1445217966578148</v>
+        <v>-0.1444608066790375</v>
       </c>
       <c r="N10" t="n">
-        <v>0.07026679819755101</v>
+        <v>0.07040872874985406</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.07200907333239835</v>
+        <v>-0.0717087411121175</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.2373758330444592</v>
+        <v>-0.2373465705124365</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.09120726527570787</v>
+        <v>0.09083335075510851</v>
       </c>
     </row>
     <row r="11">
@@ -1012,52 +1017,52 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.01987465740946477</v>
+        <v>-0.02023262583688582</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1046149505119451</v>
+        <v>0.1047921404974438</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2551667137727798</v>
+        <v>-0.2559339904157806</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01588996005253897</v>
+        <v>0.01535182619709805</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2169772356824769</v>
+        <v>-0.2172389265916096</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.02821436824340161</v>
+        <v>-0.02880036225607209</v>
       </c>
       <c r="H11" t="n">
-        <v>0.08037297457869853</v>
+        <v>0.0804204631612911</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0287803870260541</v>
+        <v>0.02874656822736521</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1561978629826447</v>
+        <v>-0.156683766267029</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1617550612319883</v>
+        <v>0.1614298105470199</v>
       </c>
       <c r="M11" t="n">
-        <v>0.07762541707322988</v>
+        <v>0.0777757365189365</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.05941020040244682</v>
+        <v>-0.05980614424136136</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2185895031115556</v>
+        <v>-0.2185679246917631</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.1828521484897391</v>
+        <v>-0.1831773585667058</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.02600774868391717</v>
+        <v>0.02546433800697261</v>
       </c>
     </row>
     <row r="12">
@@ -1067,52 +1072,52 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.2124408170959624</v>
+        <v>-0.2123027058448726</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.08171902053233267</v>
+        <v>-0.081502081581056</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1548185278472933</v>
+        <v>-0.1544177851719317</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.02670355145223416</v>
+        <v>-0.0269627133175299</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.06504378092832065</v>
+        <v>-0.06581471079996727</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.06702146799004474</v>
+        <v>-0.06702500843244734</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.04245124172712152</v>
+        <v>-0.04282791198010744</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2855608364447889</v>
+        <v>-0.2856954382706137</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.06217853777973257</v>
+        <v>-0.06216678817503089</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1617550612319883</v>
+        <v>0.1614298105470199</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.03360073897522041</v>
+        <v>-0.03242241028737669</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1437725417593451</v>
+        <v>-0.1434811993634143</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2022777279797416</v>
+        <v>-0.2020355908202672</v>
       </c>
       <c r="P12" t="n">
-        <v>0.01026397749727519</v>
+        <v>0.01033136172759034</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.129751026357779</v>
+        <v>-0.1300986436305856</v>
       </c>
     </row>
     <row r="13">
@@ -1122,52 +1127,52 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.05513312173634611</v>
+        <v>0.05537416099182556</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.003230615102660938</v>
+        <v>-0.002603634993888561</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1618051504961168</v>
+        <v>-0.1631356505068055</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.1624175403278658</v>
+        <v>-0.1599629804837387</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2320823592345288</v>
+        <v>-0.2286041614346418</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0545557848845894</v>
+        <v>0.05461928683228947</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.01825900616721546</v>
+        <v>-0.01611205899542008</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.003660810734103721</v>
+        <v>-0.003096391810210571</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.1445217966578148</v>
+        <v>-0.1444608066790375</v>
       </c>
       <c r="K13" t="n">
-        <v>0.07762541707322988</v>
+        <v>0.0777757365189365</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.03360073897522041</v>
+        <v>-0.03242241028737669</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.185499951967015</v>
+        <v>-0.1854840492147241</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.07663125096897173</v>
+        <v>-0.07652378564408509</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.1318520216812912</v>
+        <v>-0.1305778835275704</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.08808436618096037</v>
+        <v>-0.08642893441578599</v>
       </c>
     </row>
     <row r="14">
@@ -1177,52 +1182,52 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.05081185705166749</v>
+        <v>-0.05071852943701981</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.00818018298830407</v>
+        <v>-0.007848159788800862</v>
       </c>
       <c r="D14" t="n">
-        <v>0.02910181453628225</v>
+        <v>0.02933568166165289</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.3132840687800149</v>
+        <v>-0.3135756088197718</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.008296787704363637</v>
+        <v>-0.008960526192506752</v>
       </c>
       <c r="G14" t="n">
-        <v>0.09563706833332421</v>
+        <v>0.09558897275578389</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.07826192808194926</v>
+        <v>-0.07856538064548585</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2056830555769451</v>
+        <v>-0.2057101692174151</v>
       </c>
       <c r="J14" t="n">
-        <v>0.07026679819755101</v>
+        <v>0.07040872874985406</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.05941020040244682</v>
+        <v>-0.05980614424136136</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.1437725417593451</v>
+        <v>-0.1434811993634143</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.185499951967015</v>
+        <v>-0.1854840492147241</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.03264792143396295</v>
+        <v>-0.03232538476031201</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.04242172321894889</v>
+        <v>-0.04222534407186096</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.09982729717964865</v>
+        <v>-0.1000330688839532</v>
       </c>
     </row>
     <row r="15">
@@ -1232,52 +1237,52 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2399115651769097</v>
+        <v>0.2399073894964485</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1563790222364528</v>
+        <v>0.156493694081298</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1080459417212321</v>
+        <v>0.1083091976049831</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.09164567819270006</v>
+        <v>-0.09183052446789293</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1014316210031799</v>
+        <v>0.1008844494276684</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.2800088622062091</v>
+        <v>-0.2799042382213007</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1368347571769761</v>
+        <v>-0.1370775365099921</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.07742031539608377</v>
+        <v>-0.07726734613634824</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.07200907333239835</v>
+        <v>-0.0717087411121175</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.2185895031115556</v>
+        <v>-0.2185679246917631</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.2022777279797416</v>
+        <v>-0.2020355908202672</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.07663125096897173</v>
+        <v>-0.07652378564408509</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.03264792143396295</v>
+        <v>-0.03232538476031201</v>
       </c>
       <c r="O15" t="n">
         <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>0.03693455403414968</v>
+        <v>0.03724511426566401</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.3450165757294822</v>
+        <v>-0.3449961295682142</v>
       </c>
     </row>
     <row r="16">
@@ -1287,52 +1292,52 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.01159107370054597</v>
+        <v>0.011760044792132</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1736775005264178</v>
+        <v>0.1739505769284413</v>
       </c>
       <c r="D16" t="n">
-        <v>0.08450138606341739</v>
+        <v>0.08499193258261718</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.81620986443648e-05</v>
+        <v>-0.0007493378673589515</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1426307552803655</v>
+        <v>-0.143358413067378</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2232931074821536</v>
+        <v>-0.2232492729314204</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2704131965250233</v>
+        <v>-0.2707631639220237</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2650191617080321</v>
+        <v>-0.26504853568988</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.2373758330444592</v>
+        <v>-0.2373465705124365</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.1828521484897391</v>
+        <v>-0.1831773585667058</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01026397749727519</v>
+        <v>0.01033136172759034</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1318520216812912</v>
+        <v>-0.1305778835275704</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.04242172321894889</v>
+        <v>-0.04222534407186096</v>
       </c>
       <c r="O16" t="n">
-        <v>0.03693455403414968</v>
+        <v>0.03724511426566401</v>
       </c>
       <c r="P16" t="n">
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.1166083030000084</v>
+        <v>-0.1170204207530741</v>
       </c>
     </row>
     <row r="17">
@@ -1342,49 +1347,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.1475681659483614</v>
+        <v>-0.1477357341140219</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.09772647085232114</v>
+        <v>-0.09751341449245601</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1583719064520411</v>
+        <v>0.1582543841509446</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.05125591940290585</v>
+        <v>-0.0524243329062518</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1730098060318544</v>
+        <v>-0.1740479754320955</v>
       </c>
       <c r="G17" t="n">
-        <v>0.003477420104303421</v>
+        <v>0.003221320246835839</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1712785952862148</v>
+        <v>-0.1717899765930167</v>
       </c>
       <c r="I17" t="n">
-        <v>0.07427947908520935</v>
+        <v>0.07410866340476774</v>
       </c>
       <c r="J17" t="n">
-        <v>0.09120726527570787</v>
+        <v>0.09083335075510851</v>
       </c>
       <c r="K17" t="n">
-        <v>0.02600774868391717</v>
+        <v>0.02546433800697261</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.129751026357779</v>
+        <v>-0.1300986436305856</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.08808436618096037</v>
+        <v>-0.08642893441578599</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.09982729717964865</v>
+        <v>-0.1000330688839532</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3450165757294822</v>
+        <v>-0.3449961295682142</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1166083030000084</v>
+        <v>-0.1170204207530741</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
